--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2239"/>
+  <dimension ref="A1:E2240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60869,6 +60869,33 @@
         </is>
       </c>
     </row>
+    <row r="2240">
+      <c r="A2240" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B2240" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2240" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D2240" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E2240" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2240"/>
+  <dimension ref="A1:E2241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60896,6 +60896,33 @@
         </is>
       </c>
     </row>
+    <row r="2241">
+      <c r="A2241" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B2241" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2241" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D2241" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E2241" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2241"/>
+  <dimension ref="A1:E2242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60923,6 +60923,33 @@
         </is>
       </c>
     </row>
+    <row r="2242">
+      <c r="A2242" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B2242" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2242" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D2242" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E2242" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2242"/>
+  <dimension ref="A1:E2243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60950,6 +60950,33 @@
         </is>
       </c>
     </row>
+    <row r="2243">
+      <c r="A2243" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B2243" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2243" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D2243" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E2243" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2243"/>
+  <dimension ref="A1:E2244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60977,6 +60977,33 @@
         </is>
       </c>
     </row>
+    <row r="2244">
+      <c r="A2244" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B2244" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2244" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D2244" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E2244" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2244"/>
+  <dimension ref="A1:E2245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61004,6 +61004,33 @@
         </is>
       </c>
     </row>
+    <row r="2245">
+      <c r="A2245" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B2245" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2245" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D2245" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E2245" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2245"/>
+  <dimension ref="A1:E2246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61031,6 +61031,33 @@
         </is>
       </c>
     </row>
+    <row r="2246">
+      <c r="A2246" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B2246" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2246" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D2246" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E2246" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2246"/>
+  <dimension ref="A1:E2247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61058,6 +61058,33 @@
         </is>
       </c>
     </row>
+    <row r="2247">
+      <c r="A2247" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B2247" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2247" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D2247" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E2247" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2247"/>
+  <dimension ref="A1:E2248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61085,6 +61085,33 @@
         </is>
       </c>
     </row>
+    <row r="2248">
+      <c r="A2248" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B2248" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2248" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D2248" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E2248" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2248"/>
+  <dimension ref="A1:E2249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61112,6 +61112,33 @@
         </is>
       </c>
     </row>
+    <row r="2249">
+      <c r="A2249" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B2249" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2249" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D2249" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E2249" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2249"/>
+  <dimension ref="A1:E2250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61139,6 +61139,33 @@
         </is>
       </c>
     </row>
+    <row r="2250">
+      <c r="A2250" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B2250" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2250" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D2250" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="E2250" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2250"/>
+  <dimension ref="A1:E2251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61166,6 +61166,33 @@
         </is>
       </c>
     </row>
+    <row r="2251">
+      <c r="A2251" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B2251" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2251" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D2251" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E2251" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2251"/>
+  <dimension ref="A1:E2252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61193,6 +61193,33 @@
         </is>
       </c>
     </row>
+    <row r="2252">
+      <c r="A2252" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B2252" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2252" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D2252" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E2252" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2252"/>
+  <dimension ref="A1:E2253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61220,6 +61220,33 @@
         </is>
       </c>
     </row>
+    <row r="2253">
+      <c r="A2253" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B2253" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2253" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D2253" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E2253" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2253"/>
+  <dimension ref="A1:E2254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61247,6 +61247,33 @@
         </is>
       </c>
     </row>
+    <row r="2254">
+      <c r="A2254" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B2254" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2254" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D2254" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E2254" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2254"/>
+  <dimension ref="A1:E2255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61274,6 +61274,33 @@
         </is>
       </c>
     </row>
+    <row r="2255">
+      <c r="A2255" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B2255" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2255" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D2255" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E2255" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2255"/>
+  <dimension ref="A1:E2256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61301,6 +61301,33 @@
         </is>
       </c>
     </row>
+    <row r="2256">
+      <c r="A2256" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B2256" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2256" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D2256" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="E2256" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2256"/>
+  <dimension ref="A1:E2257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61328,6 +61328,33 @@
         </is>
       </c>
     </row>
+    <row r="2257">
+      <c r="A2257" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B2257" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2257" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D2257" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E2257" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2257"/>
+  <dimension ref="A1:E2258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61355,6 +61355,33 @@
         </is>
       </c>
     </row>
+    <row r="2258">
+      <c r="A2258" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B2258" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2258" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D2258" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E2258" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2258"/>
+  <dimension ref="A1:E2259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61382,6 +61382,33 @@
         </is>
       </c>
     </row>
+    <row r="2259">
+      <c r="A2259" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B2259" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2259" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D2259" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E2259" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2259"/>
+  <dimension ref="A1:E2260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61409,6 +61409,33 @@
         </is>
       </c>
     </row>
+    <row r="2260">
+      <c r="A2260" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B2260" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2260" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D2260" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E2260" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2260"/>
+  <dimension ref="A1:E2261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61436,6 +61436,33 @@
         </is>
       </c>
     </row>
+    <row r="2261">
+      <c r="A2261" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B2261" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2261" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D2261" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E2261" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2261"/>
+  <dimension ref="A1:E2262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61463,6 +61463,33 @@
         </is>
       </c>
     </row>
+    <row r="2262">
+      <c r="A2262" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B2262" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2262" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D2262" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E2262" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
